--- a/서버정보/20260921_리소스배포_테스트.xlsx
+++ b/서버정보/20260921_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9F1B9B-3A43-468D-82BF-579E39A6673F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3296B9E-B796-4D3F-B981-F82841EFF52B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4544" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4544" uniqueCount="635">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3968,10 +3968,6 @@
   </si>
   <si>
     <t>1,2,3</t>
-  </si>
-  <si>
-    <t>hazr-t-ext-vnet</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>t-dis-ap-sbn</t>
@@ -4481,7 +4477,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4831,9 +4827,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -11078,7 +11071,7 @@
       <c r="C71" s="74" t="s">
         <v>286</v>
       </c>
-      <c r="D71" s="117" t="s">
+      <c r="D71" s="74" t="s">
         <v>622</v>
       </c>
       <c r="E71" s="74" t="str">
@@ -11200,7 +11193,7 @@
       <c r="C73" s="74" t="s">
         <v>286</v>
       </c>
-      <c r="D73" s="117" t="s">
+      <c r="D73" s="74" t="s">
         <v>624</v>
       </c>
       <c r="E73" s="74" t="str">
@@ -11322,7 +11315,7 @@
       <c r="C75" s="74" t="s">
         <v>286</v>
       </c>
-      <c r="D75" s="117" t="s">
+      <c r="D75" s="74" t="s">
         <v>626</v>
       </c>
       <c r="E75" s="74" t="str">
@@ -29498,7 +29491,7 @@
       <c r="B46" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C46" s="117" t="str" cm="1">
+      <c r="C46" s="74" t="str" cm="1">
         <f t="array" ref="C46">UPPER(INDEX(_xlfn.TEXTSPLIT($F46, "-"), 3))</f>
         <v>DIS</v>
       </c>
@@ -29508,7 +29501,7 @@
       <c r="E46" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F46" s="117" t="s">
+      <c r="F46" s="74" t="s">
         <v>622</v>
       </c>
       <c r="G46" s="74" t="s">
@@ -29523,7 +29516,7 @@
       <c r="J46" s="74" t="s">
         <v>102</v>
       </c>
-      <c r="K46" s="117" t="str">
+      <c r="K46" s="74" t="str">
         <f t="shared" si="4"/>
         <v>t-dis-tmchweb-lb-fe</v>
       </c>
@@ -29533,16 +29526,16 @@
       <c r="M46" s="74" t="s">
         <v>200</v>
       </c>
-      <c r="N46" s="117" t="s">
+      <c r="N46" s="74" t="s">
         <v>290</v>
       </c>
-      <c r="O46" s="117" t="s">
+      <c r="O46" s="74" t="s">
         <v>108</v>
       </c>
-      <c r="P46" s="117" t="s">
-        <v>630</v>
-      </c>
-      <c r="Q46" s="117" t="str">
+      <c r="P46" s="74" t="s">
+        <v>629</v>
+      </c>
+      <c r="Q46" s="74" t="str">
         <f t="shared" si="5"/>
         <v>t-dis-tmchweb-lb-bp</v>
       </c>
@@ -29594,7 +29587,7 @@
         <v>108</v>
       </c>
       <c r="P47" s="84" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="Q47" s="85" t="str">
         <f t="shared" si="5"/>
@@ -29606,7 +29599,7 @@
       <c r="B48" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C48" s="117" t="str" cm="1">
+      <c r="C48" s="74" t="str" cm="1">
         <f t="array" ref="C48">UPPER(INDEX(_xlfn.TEXTSPLIT($F48, "-"), 3))</f>
         <v>DIS</v>
       </c>
@@ -29616,7 +29609,7 @@
       <c r="E48" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F48" s="117" t="s">
+      <c r="F48" s="74" t="s">
         <v>624</v>
       </c>
       <c r="G48" s="74" t="s">
@@ -29631,7 +29624,7 @@
       <c r="J48" s="74" t="s">
         <v>102</v>
       </c>
-      <c r="K48" s="117" t="str">
+      <c r="K48" s="74" t="str">
         <f t="shared" si="4"/>
         <v>t-dis-tmchintweb-lb-fe</v>
       </c>
@@ -29641,16 +29634,16 @@
       <c r="M48" s="74" t="s">
         <v>200</v>
       </c>
-      <c r="N48" s="117" t="s">
-        <v>629</v>
-      </c>
-      <c r="O48" s="117" t="s">
+      <c r="N48" s="74" t="s">
+        <v>628</v>
+      </c>
+      <c r="O48" s="74" t="s">
         <v>108</v>
       </c>
-      <c r="P48" s="117" t="s">
-        <v>632</v>
-      </c>
-      <c r="Q48" s="117" t="str">
+      <c r="P48" s="74" t="s">
+        <v>631</v>
+      </c>
+      <c r="Q48" s="74" t="str">
         <f t="shared" si="5"/>
         <v>t-dis-tmchintweb-lb-bp</v>
       </c>
@@ -29693,7 +29686,7 @@
         <v>198</v>
       </c>
       <c r="M49" s="84" t="s">
-        <v>628</v>
+        <v>199</v>
       </c>
       <c r="N49" s="84" t="s">
         <v>290</v>
@@ -29702,7 +29695,7 @@
         <v>108</v>
       </c>
       <c r="P49" s="84" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="Q49" s="85" t="str">
         <f t="shared" si="5"/>
@@ -29714,7 +29707,7 @@
       <c r="B50" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C50" s="117" t="str" cm="1">
+      <c r="C50" s="74" t="str" cm="1">
         <f t="array" ref="C50">UPPER(INDEX(_xlfn.TEXTSPLIT($F50, "-"), 3))</f>
         <v>DIS</v>
       </c>
@@ -29724,7 +29717,7 @@
       <c r="E50" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F50" s="117" t="s">
+      <c r="F50" s="74" t="s">
         <v>626</v>
       </c>
       <c r="G50" s="74" t="s">
@@ -29739,7 +29732,7 @@
       <c r="J50" s="74" t="s">
         <v>102</v>
       </c>
-      <c r="K50" s="117" t="str">
+      <c r="K50" s="74" t="str">
         <f t="shared" si="4"/>
         <v>t-dis-gaoap-lb-fe</v>
       </c>
@@ -29749,16 +29742,16 @@
       <c r="M50" s="74" t="s">
         <v>200</v>
       </c>
-      <c r="N50" s="117" t="s">
-        <v>629</v>
-      </c>
-      <c r="O50" s="117" t="s">
+      <c r="N50" s="74" t="s">
+        <v>628</v>
+      </c>
+      <c r="O50" s="74" t="s">
         <v>108</v>
       </c>
-      <c r="P50" s="117" t="s">
-        <v>634</v>
-      </c>
-      <c r="Q50" s="117" t="str">
+      <c r="P50" s="74" t="s">
+        <v>633</v>
+      </c>
+      <c r="Q50" s="74" t="str">
         <f t="shared" si="5"/>
         <v>t-dis-gaoap-lb-bp</v>
       </c>
@@ -32070,17 +32063,17 @@
       <c r="D71" s="74" t="s">
         <v>286</v>
       </c>
-      <c r="E71" s="117" t="s">
+      <c r="E71" s="74" t="s">
         <v>622</v>
       </c>
-      <c r="F71" s="117" t="str">
+      <c r="F71" s="74" t="str">
         <f t="shared" si="5"/>
         <v>t-dis-tmchweb-lb-pb443</v>
       </c>
-      <c r="G71" s="117" t="s">
-        <v>635</v>
-      </c>
-      <c r="H71" s="117">
+      <c r="G71" s="74" t="s">
+        <v>634</v>
+      </c>
+      <c r="H71" s="74">
         <v>443</v>
       </c>
       <c r="I71" s="74"/>
@@ -32111,7 +32104,7 @@
         <v>t-dis-tmchap-lb-pb8080</v>
       </c>
       <c r="G72" s="84" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H72" s="84">
         <v>8080</v>
@@ -32136,17 +32129,17 @@
       <c r="D73" s="74" t="s">
         <v>286</v>
       </c>
-      <c r="E73" s="117" t="s">
+      <c r="E73" s="74" t="s">
         <v>624</v>
       </c>
-      <c r="F73" s="117" t="str">
+      <c r="F73" s="74" t="str">
         <f t="shared" si="5"/>
         <v>t-dis-tmchintweb-lb-pb443</v>
       </c>
-      <c r="G73" s="117" t="s">
-        <v>635</v>
-      </c>
-      <c r="H73" s="117">
+      <c r="G73" s="74" t="s">
+        <v>634</v>
+      </c>
+      <c r="H73" s="74">
         <v>443</v>
       </c>
       <c r="I73" s="74"/>
@@ -32177,7 +32170,7 @@
         <v>t-dis-gaoweb-lb-pb443</v>
       </c>
       <c r="G74" s="84" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H74" s="84">
         <v>443</v>
@@ -32202,17 +32195,17 @@
       <c r="D75" s="74" t="s">
         <v>286</v>
       </c>
-      <c r="E75" s="117" t="s">
+      <c r="E75" s="74" t="s">
         <v>626</v>
       </c>
-      <c r="F75" s="117" t="str">
+      <c r="F75" s="74" t="str">
         <f t="shared" si="5"/>
         <v>t-dis-gaoap-lb-pb8080</v>
       </c>
-      <c r="G75" s="117" t="s">
-        <v>635</v>
-      </c>
-      <c r="H75" s="117">
+      <c r="G75" s="74" t="s">
+        <v>634</v>
+      </c>
+      <c r="H75" s="74">
         <v>8080</v>
       </c>
       <c r="I75" s="74"/>
@@ -32230,6 +32223,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -32373,22 +32381,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -32404,28 +32421,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/서버정보/20260921_리소스배포_테스트.xlsx
+++ b/서버정보/20260921_리소스배포_테스트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3296B9E-B796-4D3F-B981-F82841EFF52B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C274B81-557B-4CC1-AA27-4F0DDBB09A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29470,7 +29470,7 @@
         <v>198</v>
       </c>
       <c r="M45" s="84" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N45" s="84" t="s">
         <v>288</v>
@@ -29524,7 +29524,7 @@
         <v>198</v>
       </c>
       <c r="M46" s="74" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N46" s="74" t="s">
         <v>290</v>
@@ -32223,21 +32223,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -32381,31 +32366,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -32421,4 +32397,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/서버정보/20260921_리소스배포_테스트.xlsx
+++ b/서버정보/20260921_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C274B81-557B-4CC1-AA27-4F0DDBB09A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF5EC44F-1DDD-493F-BB58-23DACCBA42CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4544" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4544" uniqueCount="636">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3995,6 +3995,10 @@
   </si>
   <si>
     <t>TCP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-t-dch-ext-vnet</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -17202,10 +17206,10 @@
         <v>198</v>
       </c>
       <c r="Y63" s="113" t="s">
-        <v>450</v>
+        <v>635</v>
       </c>
       <c r="Z63" s="113" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AA63" s="107" t="b">
         <v>1</v>
@@ -17466,10 +17470,10 @@
         <v>198</v>
       </c>
       <c r="Y66" s="113" t="s">
-        <v>450</v>
+        <v>635</v>
       </c>
       <c r="Z66" s="113" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AA66" s="107" t="b">
         <v>1</v>
@@ -32223,6 +32227,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -32366,22 +32385,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -32397,28 +32425,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/서버정보/20260921_리소스배포_테스트.xlsx
+++ b/서버정보/20260921_리소스배포_테스트.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF5EC44F-1DDD-493F-BB58-23DACCBA42CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE5C1A83-54CD-4F04-93E7-2882A2F568CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4544" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4471" uniqueCount="612">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3774,117 +3774,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hazr-t-dis-rg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-dis-clvweb01</t>
-  </si>
-  <si>
-    <t>hazr-t-dis-clvap01</t>
-  </si>
-  <si>
-    <t>hazr-t-dis-clvssrap01</t>
-  </si>
-  <si>
-    <t>hazr-t-dis-clvadmweb01</t>
-  </si>
-  <si>
-    <t>hazr-t-dis-clvadmap01</t>
-  </si>
-  <si>
-    <t>10.157.128.21</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.8_Base_Image/versions/0.0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.144.131</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.144.141</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.144.151</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.144.161</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>t-dis-web-sbn</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>t-dis-ap-sbn</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-dis-clvweb01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-dis-clvap01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-dis-clvssrap01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-dis-clvadmweb01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-dis-clvadmap01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-dis-clvweb-lb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.128.20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-dis-clvap-lb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.144.130</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-dis-clvssrap-lb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.144.140</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-dis-clvadmweb-lb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.144.150</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-dis-clvadmap-lb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.144.160</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>TCP</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3904,101 +3793,120 @@
     <t>hazr-t-dis-gaoap01</t>
   </si>
   <si>
-    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.8_Base_Image/versions/0.0.5</t>
-  </si>
-  <si>
-    <t>10.157.128.51</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.128.61</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.144.51</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.144.71</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.144.171</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-dis-tmchweb01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-dis-tmchap01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-dis-tmchintweb01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-dis-gaoweb01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-dis-gaoap01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-dis-tmchweb-lb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-dis-tmchap-lb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-dis-tmchintweb-lb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-dis-gaoweb-lb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-dis-gaoap-lb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1,2,3</t>
   </si>
   <si>
-    <t>t-dis-ap-sbn</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.128.50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.144.50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.144.70</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.128.60</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.157.144.170</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>TCP</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>hazr-t-dch-ext-vnet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-t-clv-rg</t>
+  </si>
+  <si>
+    <t>10.157.133.11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.159.11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.159.21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.159.31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.159.41</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-t-clv-web01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-t-clv-ap01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-t-clv-ssrap01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-t-clv-admweb01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-t-clv-admap01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.8_Base_Image/versions/0.0.6</t>
+  </si>
+  <si>
+    <t>hazr-t-clv-rg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t-clv-web-sbn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t-clv-ap-sbn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t-clv-db-nsg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t-clv-pe-nsg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-t-clv-web-lb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-t-clv-ap-lb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-t-clv-ssrap-lb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-t-clv-admweb-lb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-t-clv-admap-lb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.133.10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.159.10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.159.20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.159.30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.157.159.40</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4481,7 +4389,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4832,6 +4740,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10765,21 +10682,21 @@
       </c>
       <c r="B66" s="84" t="str" cm="1">
         <f t="array" ref="B66">UPPER(INDEX(_xlfn.TEXTSPLIT($C66, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="C66" s="84" t="s">
-        <v>286</v>
+        <v>597</v>
       </c>
       <c r="D66" s="84" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="E66" s="84" t="str">
         <f t="shared" si="24"/>
-        <v>t-dis-clvweb-lb-rule443</v>
+        <v>t-clv-web-lb-rule443</v>
       </c>
       <c r="F66" s="84" t="str">
         <f t="shared" si="29"/>
-        <v>t-dis-clvweb-lb-fe</v>
+        <v>t-clv-web-lb-fe</v>
       </c>
       <c r="G66" s="84" t="s">
         <v>57</v>
@@ -10792,14 +10709,14 @@
       </c>
       <c r="J66" s="84" t="str">
         <f t="shared" si="30"/>
-        <v>t-dis-clvweb-lb-bp</v>
+        <v>t-clv-web-lb-bp</v>
       </c>
       <c r="K66" s="84">
         <v>443</v>
       </c>
       <c r="L66" s="84" t="str">
         <f t="shared" si="31"/>
-        <v>t-dis-clvweb-lb-pb443</v>
+        <v>t-clv-web-lb-pb443</v>
       </c>
       <c r="M66" s="84" t="s">
         <v>57</v>
@@ -10826,21 +10743,21 @@
       </c>
       <c r="B67" s="74" t="str" cm="1">
         <f t="array" ref="B67">UPPER(INDEX(_xlfn.TEXTSPLIT($C67, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="C67" s="74" t="s">
-        <v>286</v>
+        <v>597</v>
       </c>
       <c r="D67" s="74" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="E67" s="74" t="str">
         <f t="shared" si="28"/>
-        <v>t-dis-clvap-lb-rule8080</v>
+        <v>t-clv-ap-lb-rule8080</v>
       </c>
       <c r="F67" s="74" t="str">
         <f t="shared" ref="F67:F70" si="36">SUBSTITUTE(D67, "hazr-", "")&amp;"-fe"</f>
-        <v>t-dis-clvap-lb-fe</v>
+        <v>t-clv-ap-lb-fe</v>
       </c>
       <c r="G67" s="74" t="s">
         <v>57</v>
@@ -10853,14 +10770,14 @@
       </c>
       <c r="J67" s="74" t="str">
         <f t="shared" ref="J67:J70" si="37">SUBSTITUTE(D67, "hazr-", "")&amp;"-bp"</f>
-        <v>t-dis-clvap-lb-bp</v>
+        <v>t-clv-ap-lb-bp</v>
       </c>
       <c r="K67" s="74">
         <v>8080</v>
       </c>
       <c r="L67" s="74" t="str">
         <f t="shared" ref="L67:L70" si="38">SUBSTITUTE(D67, "hazr-", "")&amp;"-pb"&amp;IF(N67="", "", N67)</f>
-        <v>t-dis-clvap-lb-pb8080</v>
+        <v>t-clv-ap-lb-pb8080</v>
       </c>
       <c r="M67" s="74" t="s">
         <v>57</v>
@@ -10887,21 +10804,21 @@
       </c>
       <c r="B68" s="84" t="str" cm="1">
         <f t="array" ref="B68">UPPER(INDEX(_xlfn.TEXTSPLIT($C68, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="C68" s="84" t="s">
-        <v>286</v>
+        <v>597</v>
       </c>
       <c r="D68" s="84" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="E68" s="84" t="str">
         <f t="shared" si="24"/>
-        <v>t-dis-clvssrap-lb-rule8080</v>
+        <v>t-clv-ssrap-lb-rule8080</v>
       </c>
       <c r="F68" s="84" t="str">
         <f t="shared" si="36"/>
-        <v>t-dis-clvssrap-lb-fe</v>
+        <v>t-clv-ssrap-lb-fe</v>
       </c>
       <c r="G68" s="84" t="s">
         <v>57</v>
@@ -10914,14 +10831,14 @@
       </c>
       <c r="J68" s="84" t="str">
         <f t="shared" si="37"/>
-        <v>t-dis-clvssrap-lb-bp</v>
+        <v>t-clv-ssrap-lb-bp</v>
       </c>
       <c r="K68" s="84">
         <v>8080</v>
       </c>
       <c r="L68" s="84" t="str">
         <f t="shared" si="38"/>
-        <v>t-dis-clvssrap-lb-pb8080</v>
+        <v>t-clv-ssrap-lb-pb8080</v>
       </c>
       <c r="M68" s="84" t="s">
         <v>57</v>
@@ -10948,21 +10865,21 @@
       </c>
       <c r="B69" s="74" t="str" cm="1">
         <f t="array" ref="B69">UPPER(INDEX(_xlfn.TEXTSPLIT($C69, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="C69" s="74" t="s">
-        <v>286</v>
-      </c>
-      <c r="D69" s="74" t="s">
-        <v>601</v>
+        <v>597</v>
+      </c>
+      <c r="D69" s="107" t="s">
+        <v>605</v>
       </c>
       <c r="E69" s="74" t="str">
         <f t="shared" si="28"/>
-        <v>t-dis-clvadmweb-lb-rule443</v>
+        <v>t-clv-admweb-lb-rule443</v>
       </c>
       <c r="F69" s="74" t="str">
         <f t="shared" si="36"/>
-        <v>t-dis-clvadmweb-lb-fe</v>
+        <v>t-clv-admweb-lb-fe</v>
       </c>
       <c r="G69" s="74" t="s">
         <v>57</v>
@@ -10975,14 +10892,14 @@
       </c>
       <c r="J69" s="74" t="str">
         <f t="shared" si="37"/>
-        <v>t-dis-clvadmweb-lb-bp</v>
+        <v>t-clv-admweb-lb-bp</v>
       </c>
       <c r="K69" s="74">
         <v>443</v>
       </c>
       <c r="L69" s="74" t="str">
         <f t="shared" si="38"/>
-        <v>t-dis-clvadmweb-lb-pb443</v>
+        <v>t-clv-admweb-lb-pb443</v>
       </c>
       <c r="M69" s="74" t="s">
         <v>57</v>
@@ -11009,21 +10926,21 @@
       </c>
       <c r="B70" s="84" t="str" cm="1">
         <f t="array" ref="B70">UPPER(INDEX(_xlfn.TEXTSPLIT($C70, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="C70" s="84" t="s">
-        <v>286</v>
+        <v>597</v>
       </c>
       <c r="D70" s="84" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="E70" s="84" t="str">
         <f t="shared" si="24"/>
-        <v>t-dis-clvadmap-lb-rule8080</v>
+        <v>t-clv-admap-lb-rule8080</v>
       </c>
       <c r="F70" s="84" t="str">
         <f t="shared" si="36"/>
-        <v>t-dis-clvadmap-lb-fe</v>
+        <v>t-clv-admap-lb-fe</v>
       </c>
       <c r="G70" s="84" t="s">
         <v>57</v>
@@ -11036,14 +10953,14 @@
       </c>
       <c r="J70" s="84" t="str">
         <f t="shared" si="37"/>
-        <v>t-dis-clvadmap-lb-bp</v>
+        <v>t-clv-admap-lb-bp</v>
       </c>
       <c r="K70" s="84">
         <v>8080</v>
       </c>
       <c r="L70" s="84" t="str">
         <f t="shared" si="38"/>
-        <v>t-dis-clvadmap-lb-pb8080</v>
+        <v>t-clv-admap-lb-pb8080</v>
       </c>
       <c r="M70" s="84" t="s">
         <v>57</v>
@@ -11068,23 +10985,19 @@
       <c r="A71" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="B71" s="74" t="str" cm="1">
+      <c r="B71" s="74" t="e" cm="1">
         <f t="array" ref="B71">UPPER(INDEX(_xlfn.TEXTSPLIT($C71, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="C71" s="74" t="s">
-        <v>286</v>
-      </c>
-      <c r="D71" s="74" t="s">
-        <v>622</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C71" s="74"/>
+      <c r="D71" s="74"/>
       <c r="E71" s="74" t="str">
         <f t="shared" si="24"/>
-        <v>t-dis-tmchweb-lb-rule443</v>
+        <v>-rule443</v>
       </c>
       <c r="F71" s="74" t="str">
         <f t="shared" ref="F71:F75" si="39">SUBSTITUTE(D71, "hazr-", "")&amp;"-fe"</f>
-        <v>t-dis-tmchweb-lb-fe</v>
+        <v>-fe</v>
       </c>
       <c r="G71" s="74" t="s">
         <v>57</v>
@@ -11097,14 +11010,14 @@
       </c>
       <c r="J71" s="74" t="str">
         <f t="shared" ref="J71:J75" si="40">SUBSTITUTE(D71, "hazr-", "")&amp;"-bp"</f>
-        <v>t-dis-tmchweb-lb-bp</v>
+        <v>-bp</v>
       </c>
       <c r="K71" s="74">
         <v>443</v>
       </c>
       <c r="L71" s="74" t="str">
         <f t="shared" ref="L71:L75" si="41">SUBSTITUTE(D71, "hazr-", "")&amp;"-pb"&amp;IF(N71="", "", N71)</f>
-        <v>t-dis-tmchweb-lb-pb443</v>
+        <v>-pb443</v>
       </c>
       <c r="M71" s="74" t="s">
         <v>57</v>
@@ -11129,23 +11042,19 @@
       <c r="A72" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="B72" s="84" t="str" cm="1">
+      <c r="B72" s="84" t="e" cm="1">
         <f t="array" ref="B72">UPPER(INDEX(_xlfn.TEXTSPLIT($C72, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="C72" s="84" t="s">
-        <v>286</v>
-      </c>
-      <c r="D72" s="84" t="s">
-        <v>623</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C72" s="84"/>
+      <c r="D72" s="84"/>
       <c r="E72" s="84" t="str">
         <f t="shared" ref="E72:E75" si="42">SUBSTITUTE(D72, "hazr-", "")&amp;"-rule"&amp;N72</f>
-        <v>t-dis-tmchap-lb-rule8080</v>
+        <v>-rule8080</v>
       </c>
       <c r="F72" s="84" t="str">
         <f t="shared" si="39"/>
-        <v>t-dis-tmchap-lb-fe</v>
+        <v>-fe</v>
       </c>
       <c r="G72" s="84" t="s">
         <v>57</v>
@@ -11158,14 +11067,14 @@
       </c>
       <c r="J72" s="84" t="str">
         <f t="shared" si="40"/>
-        <v>t-dis-tmchap-lb-bp</v>
+        <v>-bp</v>
       </c>
       <c r="K72" s="84">
         <v>8080</v>
       </c>
       <c r="L72" s="84" t="str">
         <f t="shared" si="41"/>
-        <v>t-dis-tmchap-lb-pb8080</v>
+        <v>-pb8080</v>
       </c>
       <c r="M72" s="84" t="s">
         <v>57</v>
@@ -11190,23 +11099,19 @@
       <c r="A73" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="B73" s="74" t="str" cm="1">
+      <c r="B73" s="74" t="e" cm="1">
         <f t="array" ref="B73">UPPER(INDEX(_xlfn.TEXTSPLIT($C73, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="C73" s="74" t="s">
-        <v>286</v>
-      </c>
-      <c r="D73" s="74" t="s">
-        <v>624</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C73" s="74"/>
+      <c r="D73" s="74"/>
       <c r="E73" s="74" t="str">
         <f t="shared" si="42"/>
-        <v>t-dis-tmchintweb-lb-rule443</v>
+        <v>-rule443</v>
       </c>
       <c r="F73" s="74" t="str">
         <f t="shared" si="39"/>
-        <v>t-dis-tmchintweb-lb-fe</v>
+        <v>-fe</v>
       </c>
       <c r="G73" s="74" t="s">
         <v>57</v>
@@ -11219,14 +11124,14 @@
       </c>
       <c r="J73" s="74" t="str">
         <f t="shared" si="40"/>
-        <v>t-dis-tmchintweb-lb-bp</v>
+        <v>-bp</v>
       </c>
       <c r="K73" s="74">
         <v>443</v>
       </c>
       <c r="L73" s="74" t="str">
         <f t="shared" si="41"/>
-        <v>t-dis-tmchintweb-lb-pb443</v>
+        <v>-pb443</v>
       </c>
       <c r="M73" s="74" t="s">
         <v>57</v>
@@ -11251,23 +11156,19 @@
       <c r="A74" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="B74" s="84" t="str" cm="1">
+      <c r="B74" s="84" t="e" cm="1">
         <f t="array" ref="B74">UPPER(INDEX(_xlfn.TEXTSPLIT($C74, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="C74" s="84" t="s">
-        <v>286</v>
-      </c>
-      <c r="D74" s="84" t="s">
-        <v>625</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C74" s="84"/>
+      <c r="D74" s="84"/>
       <c r="E74" s="84" t="str">
         <f t="shared" si="42"/>
-        <v>t-dis-gaoweb-lb-rule443</v>
+        <v>-rule443</v>
       </c>
       <c r="F74" s="84" t="str">
         <f t="shared" si="39"/>
-        <v>t-dis-gaoweb-lb-fe</v>
+        <v>-fe</v>
       </c>
       <c r="G74" s="84" t="s">
         <v>57</v>
@@ -11280,14 +11181,14 @@
       </c>
       <c r="J74" s="84" t="str">
         <f t="shared" si="40"/>
-        <v>t-dis-gaoweb-lb-bp</v>
+        <v>-bp</v>
       </c>
       <c r="K74" s="84">
         <v>443</v>
       </c>
       <c r="L74" s="84" t="str">
         <f t="shared" si="41"/>
-        <v>t-dis-gaoweb-lb-pb443</v>
+        <v>-pb443</v>
       </c>
       <c r="M74" s="84" t="s">
         <v>57</v>
@@ -11312,23 +11213,19 @@
       <c r="A75" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="B75" s="74" t="str" cm="1">
+      <c r="B75" s="74" t="e" cm="1">
         <f t="array" ref="B75">UPPER(INDEX(_xlfn.TEXTSPLIT($C75, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="C75" s="74" t="s">
-        <v>286</v>
-      </c>
-      <c r="D75" s="74" t="s">
-        <v>626</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C75" s="74"/>
+      <c r="D75" s="74"/>
       <c r="E75" s="74" t="str">
         <f t="shared" si="42"/>
-        <v>t-dis-gaoap-lb-rule8080</v>
+        <v>-rule8080</v>
       </c>
       <c r="F75" s="74" t="str">
         <f t="shared" si="39"/>
-        <v>t-dis-gaoap-lb-fe</v>
+        <v>-fe</v>
       </c>
       <c r="G75" s="74" t="s">
         <v>57</v>
@@ -11341,14 +11238,14 @@
       </c>
       <c r="J75" s="74" t="str">
         <f t="shared" si="40"/>
-        <v>t-dis-gaoap-lb-bp</v>
+        <v>-bp</v>
       </c>
       <c r="K75" s="74">
         <v>8080</v>
       </c>
       <c r="L75" s="74" t="str">
         <f t="shared" si="41"/>
-        <v>t-dis-gaoap-lb-pb8080</v>
+        <v>-pb8080</v>
       </c>
       <c r="M75" s="74" t="s">
         <v>57</v>
@@ -16694,25 +16591,25 @@
       <c r="AF57" s="107"/>
     </row>
     <row r="58" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A58" s="97"/>
+      <c r="A58" s="117"/>
       <c r="B58" s="107" t="s">
         <v>575</v>
       </c>
       <c r="C58" s="107" t="str" cm="1">
         <f t="array" ref="C58">UPPER(INDEX(_xlfn.TEXTSPLIT($D58, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D58" s="107" t="s">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="E58" s="107" t="s">
         <v>24</v>
       </c>
       <c r="F58" s="107" t="s">
-        <v>577</v>
+        <v>591</v>
       </c>
       <c r="G58" s="107" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="H58" s="108" t="s">
         <v>179</v>
@@ -16733,11 +16630,11 @@
         <v>521</v>
       </c>
       <c r="N58" s="110" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
       <c r="O58" s="107" t="str">
         <f t="shared" ref="O58:O62" si="8">SUBSTITUTE(F58,"hazr-","")&amp;"-osdisk"</f>
-        <v>t-dis-clvweb01-osdisk</v>
+        <v>t-clv-web01-osdisk</v>
       </c>
       <c r="P58" s="107">
         <v>64</v>
@@ -16750,7 +16647,7 @@
       <c r="T58" s="107"/>
       <c r="U58" s="107" t="str">
         <f t="shared" ref="U58:U62" si="9">SUBSTITUTE(F58,"hazr-","")&amp;"-nic"</f>
-        <v>t-dis-clvweb01-nic</v>
+        <v>t-clv-web01-nic</v>
       </c>
       <c r="V58" s="107" t="b">
         <v>1</v>
@@ -16765,7 +16662,7 @@
         <v>451</v>
       </c>
       <c r="Z58" s="107" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="AA58" s="107" t="b">
         <v>1</v>
@@ -16783,25 +16680,25 @@
       <c r="AF58" s="107"/>
     </row>
     <row r="59" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A59" s="97"/>
+      <c r="A59" s="117"/>
       <c r="B59" s="113" t="s">
         <v>575</v>
       </c>
       <c r="C59" s="107" t="str" cm="1">
         <f t="array" ref="C59">UPPER(INDEX(_xlfn.TEXTSPLIT($D59, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D59" s="113" t="s">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="E59" s="113" t="s">
         <v>24</v>
       </c>
       <c r="F59" s="113" t="s">
-        <v>578</v>
+        <v>592</v>
       </c>
       <c r="G59" s="113" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="H59" s="114" t="s">
         <v>179</v>
@@ -16822,11 +16719,11 @@
         <v>521</v>
       </c>
       <c r="N59" s="110" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
       <c r="O59" s="113" t="str">
         <f t="shared" si="8"/>
-        <v>t-dis-clvap01-osdisk</v>
+        <v>t-clv-ap01-osdisk</v>
       </c>
       <c r="P59" s="107">
         <v>64</v>
@@ -16839,7 +16736,7 @@
       <c r="T59" s="113"/>
       <c r="U59" s="113" t="str">
         <f t="shared" si="9"/>
-        <v>t-dis-clvap01-nic</v>
+        <v>t-clv-ap01-nic</v>
       </c>
       <c r="V59" s="107" t="b">
         <v>1</v>
@@ -16854,7 +16751,7 @@
         <v>450</v>
       </c>
       <c r="Z59" s="113" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="AA59" s="107" t="b">
         <v>1</v>
@@ -16872,25 +16769,25 @@
       <c r="AF59" s="113"/>
     </row>
     <row r="60" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A60" s="97"/>
+      <c r="A60" s="117"/>
       <c r="B60" s="113" t="s">
         <v>575</v>
       </c>
       <c r="C60" s="107" t="str" cm="1">
         <f t="array" ref="C60">UPPER(INDEX(_xlfn.TEXTSPLIT($D60, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D60" s="107" t="s">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="E60" s="113" t="s">
         <v>24</v>
       </c>
       <c r="F60" s="113" t="s">
-        <v>579</v>
+        <v>593</v>
       </c>
       <c r="G60" s="113" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="H60" s="114" t="s">
         <v>179</v>
@@ -16911,11 +16808,11 @@
         <v>521</v>
       </c>
       <c r="N60" s="110" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
       <c r="O60" s="113" t="str">
         <f t="shared" si="8"/>
-        <v>t-dis-clvssrap01-osdisk</v>
+        <v>t-clv-ssrap01-osdisk</v>
       </c>
       <c r="P60" s="107">
         <v>64</v>
@@ -16928,7 +16825,7 @@
       <c r="T60" s="113"/>
       <c r="U60" s="113" t="str">
         <f t="shared" si="9"/>
-        <v>t-dis-clvssrap01-nic</v>
+        <v>t-clv-ssrap01-nic</v>
       </c>
       <c r="V60" s="107" t="b">
         <v>1</v>
@@ -16943,7 +16840,7 @@
         <v>450</v>
       </c>
       <c r="Z60" s="113" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="AA60" s="107" t="b">
         <v>1</v>
@@ -16961,25 +16858,25 @@
       <c r="AF60" s="113"/>
     </row>
     <row r="61" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A61" s="97"/>
+      <c r="A61" s="117"/>
       <c r="B61" s="113" t="s">
         <v>575</v>
       </c>
       <c r="C61" s="107" t="str" cm="1">
         <f t="array" ref="C61">UPPER(INDEX(_xlfn.TEXTSPLIT($D61, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D61" s="113" t="s">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="E61" s="113" t="s">
         <v>24</v>
       </c>
       <c r="F61" s="113" t="s">
-        <v>580</v>
+        <v>594</v>
       </c>
       <c r="G61" s="113" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="H61" s="114" t="s">
         <v>179</v>
@@ -17000,11 +16897,11 @@
         <v>521</v>
       </c>
       <c r="N61" s="110" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
       <c r="O61" s="113" t="str">
         <f t="shared" si="8"/>
-        <v>t-dis-clvadmweb01-osdisk</v>
+        <v>t-clv-admweb01-osdisk</v>
       </c>
       <c r="P61" s="107">
         <v>64</v>
@@ -17017,7 +16914,7 @@
       <c r="T61" s="113"/>
       <c r="U61" s="113" t="str">
         <f t="shared" si="9"/>
-        <v>t-dis-clvadmweb01-nic</v>
+        <v>t-clv-admweb01-nic</v>
       </c>
       <c r="V61" s="107" t="b">
         <v>1</v>
@@ -17032,7 +16929,7 @@
         <v>450</v>
       </c>
       <c r="Z61" s="113" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="AA61" s="107" t="b">
         <v>1</v>
@@ -17050,25 +16947,25 @@
       <c r="AF61" s="113"/>
     </row>
     <row r="62" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A62" s="97"/>
+      <c r="A62" s="117"/>
       <c r="B62" s="113" t="s">
         <v>575</v>
       </c>
       <c r="C62" s="107" t="str" cm="1">
         <f t="array" ref="C62">UPPER(INDEX(_xlfn.TEXTSPLIT($D62, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D62" s="107" t="s">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="E62" s="113" t="s">
         <v>24</v>
       </c>
       <c r="F62" s="113" t="s">
-        <v>581</v>
+        <v>595</v>
       </c>
       <c r="G62" s="113" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="H62" s="114" t="s">
         <v>179</v>
@@ -17089,11 +16986,11 @@
         <v>521</v>
       </c>
       <c r="N62" s="111" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
       <c r="O62" s="113" t="str">
         <f t="shared" si="8"/>
-        <v>t-dis-clvadmap01-osdisk</v>
+        <v>t-clv-admap01-osdisk</v>
       </c>
       <c r="P62" s="107">
         <v>64</v>
@@ -17106,7 +17003,7 @@
       <c r="T62" s="113"/>
       <c r="U62" s="113" t="str">
         <f t="shared" si="9"/>
-        <v>t-dis-clvadmap01-nic</v>
+        <v>t-clv-admap01-nic</v>
       </c>
       <c r="V62" s="107" t="b">
         <v>1</v>
@@ -17121,7 +17018,7 @@
         <v>450</v>
       </c>
       <c r="Z62" s="113" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="AA62" s="107" t="b">
         <v>1</v>
@@ -17142,22 +17039,18 @@
       <c r="B63" s="107" t="s">
         <v>182</v>
       </c>
-      <c r="C63" s="107" t="str" cm="1">
+      <c r="C63" s="107" t="e" cm="1">
         <f t="array" ref="C63">UPPER(INDEX(_xlfn.TEXTSPLIT($D63, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="D63" s="113" t="s">
-        <v>286</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D63" s="113"/>
       <c r="E63" s="107" t="s">
         <v>24</v>
       </c>
       <c r="F63" s="78" t="s">
-        <v>606</v>
-      </c>
-      <c r="G63" s="107" t="s">
-        <v>612</v>
-      </c>
+        <v>577</v>
+      </c>
+      <c r="G63" s="107"/>
       <c r="H63" s="114" t="s">
         <v>513</v>
       </c>
@@ -17176,9 +17069,7 @@
       <c r="M63" s="109" t="s">
         <v>521</v>
       </c>
-      <c r="N63" s="110" t="s">
-        <v>611</v>
-      </c>
+      <c r="N63" s="110"/>
       <c r="O63" s="107" t="str">
         <f t="shared" ref="O63:O67" si="10">SUBSTITUTE(F63,"hazr-","")&amp;"-osdisk"</f>
         <v>t-dis-tmchweb01-osdisk</v>
@@ -17206,11 +17097,9 @@
         <v>198</v>
       </c>
       <c r="Y63" s="113" t="s">
-        <v>635</v>
-      </c>
-      <c r="Z63" s="113" t="s">
-        <v>290</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="Z63" s="113"/>
       <c r="AA63" s="107" t="b">
         <v>1</v>
       </c>
@@ -17230,22 +17119,18 @@
       <c r="B64" s="113" t="s">
         <v>182</v>
       </c>
-      <c r="C64" s="107" t="str" cm="1">
+      <c r="C64" s="107" t="e" cm="1">
         <f t="array" ref="C64">UPPER(INDEX(_xlfn.TEXTSPLIT($D64, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="D64" s="107" t="s">
-        <v>286</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D64" s="107"/>
       <c r="E64" s="113" t="s">
         <v>24</v>
       </c>
       <c r="F64" s="73" t="s">
-        <v>607</v>
-      </c>
-      <c r="G64" s="113" t="s">
-        <v>614</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="G64" s="113"/>
       <c r="H64" s="114" t="s">
         <v>513</v>
       </c>
@@ -17264,9 +17149,7 @@
       <c r="M64" s="109" t="s">
         <v>521</v>
       </c>
-      <c r="N64" s="111" t="s">
-        <v>611</v>
-      </c>
+      <c r="N64" s="111"/>
       <c r="O64" s="113" t="str">
         <f t="shared" si="10"/>
         <v>t-dis-tmchap01-osdisk</v>
@@ -17296,9 +17179,7 @@
       <c r="Y64" s="113" t="s">
         <v>450</v>
       </c>
-      <c r="Z64" s="113" t="s">
-        <v>288</v>
-      </c>
+      <c r="Z64" s="113"/>
       <c r="AA64" s="107" t="b">
         <v>1</v>
       </c>
@@ -17318,22 +17199,18 @@
       <c r="B65" s="113" t="s">
         <v>182</v>
       </c>
-      <c r="C65" s="107" t="str" cm="1">
+      <c r="C65" s="107" t="e" cm="1">
         <f t="array" ref="C65">UPPER(INDEX(_xlfn.TEXTSPLIT($D65, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="D65" s="113" t="s">
-        <v>286</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D65" s="113"/>
       <c r="E65" s="113" t="s">
         <v>24</v>
       </c>
       <c r="F65" s="78" t="s">
-        <v>608</v>
-      </c>
-      <c r="G65" s="113" t="s">
-        <v>615</v>
-      </c>
+        <v>579</v>
+      </c>
+      <c r="G65" s="113"/>
       <c r="H65" s="114" t="s">
         <v>513</v>
       </c>
@@ -17352,9 +17229,7 @@
       <c r="M65" s="109" t="s">
         <v>521</v>
       </c>
-      <c r="N65" s="110" t="s">
-        <v>611</v>
-      </c>
+      <c r="N65" s="110"/>
       <c r="O65" s="113" t="str">
         <f t="shared" si="10"/>
         <v>t-dis-tmchintweb01-osdisk</v>
@@ -17384,9 +17259,7 @@
       <c r="Y65" s="113" t="s">
         <v>450</v>
       </c>
-      <c r="Z65" s="113" t="s">
-        <v>288</v>
-      </c>
+      <c r="Z65" s="113"/>
       <c r="AA65" s="107" t="b">
         <v>1</v>
       </c>
@@ -17406,22 +17279,18 @@
       <c r="B66" s="113" t="s">
         <v>182</v>
       </c>
-      <c r="C66" s="107" t="str" cm="1">
+      <c r="C66" s="107" t="e" cm="1">
         <f t="array" ref="C66">UPPER(INDEX(_xlfn.TEXTSPLIT($D66, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="D66" s="107" t="s">
-        <v>286</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D66" s="107"/>
       <c r="E66" s="113" t="s">
         <v>24</v>
       </c>
       <c r="F66" s="73" t="s">
-        <v>609</v>
-      </c>
-      <c r="G66" s="113" t="s">
-        <v>613</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="G66" s="113"/>
       <c r="H66" s="114" t="s">
         <v>513</v>
       </c>
@@ -17440,9 +17309,7 @@
       <c r="M66" s="109" t="s">
         <v>521</v>
       </c>
-      <c r="N66" s="111" t="s">
-        <v>611</v>
-      </c>
+      <c r="N66" s="111"/>
       <c r="O66" s="113" t="str">
         <f t="shared" si="10"/>
         <v>t-dis-gaoweb01-osdisk</v>
@@ -17470,11 +17337,9 @@
         <v>198</v>
       </c>
       <c r="Y66" s="113" t="s">
-        <v>635</v>
-      </c>
-      <c r="Z66" s="113" t="s">
-        <v>290</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="Z66" s="113"/>
       <c r="AA66" s="107" t="b">
         <v>1</v>
       </c>
@@ -17494,22 +17359,18 @@
       <c r="B67" s="113" t="s">
         <v>182</v>
       </c>
-      <c r="C67" s="107" t="str" cm="1">
+      <c r="C67" s="107" t="e" cm="1">
         <f t="array" ref="C67">UPPER(INDEX(_xlfn.TEXTSPLIT($D67, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="D67" s="113" t="s">
-        <v>286</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D67" s="113"/>
       <c r="E67" s="113" t="s">
         <v>24</v>
       </c>
       <c r="F67" s="115" t="s">
-        <v>610</v>
-      </c>
-      <c r="G67" s="113" t="s">
-        <v>616</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="G67" s="113"/>
       <c r="H67" s="114" t="s">
         <v>513</v>
       </c>
@@ -17528,9 +17389,7 @@
       <c r="M67" s="109" t="s">
         <v>521</v>
       </c>
-      <c r="N67" s="110" t="s">
-        <v>611</v>
-      </c>
+      <c r="N67" s="110"/>
       <c r="O67" s="113" t="str">
         <f t="shared" si="10"/>
         <v>t-dis-gaoap01-osdisk</v>
@@ -17560,9 +17419,7 @@
       <c r="Y67" s="113" t="s">
         <v>450</v>
       </c>
-      <c r="Z67" s="113" t="s">
-        <v>288</v>
-      </c>
+      <c r="Z67" s="113"/>
       <c r="AA67" s="107" t="b">
         <v>1</v>
       </c>
@@ -20747,26 +20604,26 @@
       <c r="R57" s="73"/>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A58" s="98"/>
+      <c r="A58" s="118"/>
       <c r="B58" s="74" t="s">
         <v>182</v>
       </c>
       <c r="C58" s="74" t="str" cm="1">
         <f t="array" ref="C58">UPPER(INDEX(_xlfn.TEXTSPLIT($D58, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D58" s="74" t="s">
-        <v>286</v>
+        <v>597</v>
       </c>
       <c r="E58" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F58" s="74" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="G58" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-dis-clvweb01-disk01</v>
+        <v>t-clv-web01-disk01</v>
       </c>
       <c r="H58" s="74" t="s">
         <v>181</v>
@@ -20776,7 +20633,7 @@
       </c>
       <c r="J58" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-clvweb01-disk02</v>
+        <v>t-clv-web01-disk02</v>
       </c>
       <c r="K58" s="74" t="s">
         <v>181</v>
@@ -20802,26 +20659,26 @@
       <c r="R58" s="74"/>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A59" s="98"/>
+      <c r="A59" s="118"/>
       <c r="B59" s="73" t="s">
         <v>182</v>
       </c>
       <c r="C59" s="73" t="str" cm="1">
         <f t="array" ref="C59">UPPER(INDEX(_xlfn.TEXTSPLIT($D59, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D59" s="73" t="s">
-        <v>286</v>
+        <v>597</v>
       </c>
       <c r="E59" s="73" t="s">
         <v>24</v>
       </c>
       <c r="F59" s="73" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="G59" s="73" t="str">
         <f t="shared" si="4"/>
-        <v>t-dis-clvap01-disk01</v>
+        <v>t-clv-ap01-disk01</v>
       </c>
       <c r="H59" s="73" t="s">
         <v>181</v>
@@ -20831,7 +20688,7 @@
       </c>
       <c r="J59" s="73" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-clvap01-disk02</v>
+        <v>t-clv-ap01-disk02</v>
       </c>
       <c r="K59" s="73" t="s">
         <v>181</v>
@@ -20857,26 +20714,26 @@
       <c r="R59" s="73"/>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A60" s="98"/>
+      <c r="A60" s="118"/>
       <c r="B60" s="74" t="s">
         <v>182</v>
       </c>
       <c r="C60" s="74" t="str" cm="1">
         <f t="array" ref="C60">UPPER(INDEX(_xlfn.TEXTSPLIT($D60, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D60" s="74" t="s">
-        <v>286</v>
+        <v>597</v>
       </c>
       <c r="E60" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F60" s="74" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="G60" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-dis-clvssrap01-disk01</v>
+        <v>t-clv-ssrap01-disk01</v>
       </c>
       <c r="H60" s="74" t="s">
         <v>181</v>
@@ -20886,7 +20743,7 @@
       </c>
       <c r="J60" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-clvssrap01-disk02</v>
+        <v>t-clv-ssrap01-disk02</v>
       </c>
       <c r="K60" s="74" t="s">
         <v>181</v>
@@ -20912,26 +20769,26 @@
       <c r="R60" s="74"/>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A61" s="98"/>
+      <c r="A61" s="118"/>
       <c r="B61" s="73" t="s">
         <v>182</v>
       </c>
       <c r="C61" s="73" t="str" cm="1">
         <f t="array" ref="C61">UPPER(INDEX(_xlfn.TEXTSPLIT($D61, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D61" s="73" t="s">
-        <v>286</v>
+        <v>597</v>
       </c>
       <c r="E61" s="73" t="s">
         <v>24</v>
       </c>
       <c r="F61" s="73" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="G61" s="73" t="str">
         <f t="shared" si="4"/>
-        <v>t-dis-clvadmweb01-disk01</v>
+        <v>t-clv-admweb01-disk01</v>
       </c>
       <c r="H61" s="73" t="s">
         <v>181</v>
@@ -20941,7 +20798,7 @@
       </c>
       <c r="J61" s="73" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-clvadmweb01-disk02</v>
+        <v>t-clv-admweb01-disk02</v>
       </c>
       <c r="K61" s="73" t="s">
         <v>181</v>
@@ -20967,26 +20824,26 @@
       <c r="R61" s="73"/>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A62" s="98"/>
+      <c r="A62" s="118"/>
       <c r="B62" s="74" t="s">
         <v>182</v>
       </c>
       <c r="C62" s="74" t="str" cm="1">
         <f t="array" ref="C62">UPPER(INDEX(_xlfn.TEXTSPLIT($D62, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D62" s="74" t="s">
-        <v>286</v>
+        <v>597</v>
       </c>
       <c r="E62" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F62" s="74" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="G62" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-dis-clvadmap01-disk01</v>
+        <v>t-clv-admap01-disk01</v>
       </c>
       <c r="H62" s="74" t="s">
         <v>181</v>
@@ -20996,7 +20853,7 @@
       </c>
       <c r="J62" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-clvadmap01-disk02</v>
+        <v>t-clv-admap01-disk02</v>
       </c>
       <c r="K62" s="74" t="s">
         <v>181</v>
@@ -21025,22 +20882,18 @@
       <c r="B63" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="C63" s="73" t="str" cm="1">
+      <c r="C63" s="73" t="e" cm="1">
         <f t="array" ref="C63">UPPER(INDEX(_xlfn.TEXTSPLIT($D63, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="D63" s="73" t="s">
-        <v>286</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D63" s="73"/>
       <c r="E63" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="F63" s="73" t="s">
-        <v>617</v>
-      </c>
+      <c r="F63" s="73"/>
       <c r="G63" s="73" t="str">
         <f t="shared" si="4"/>
-        <v>t-dis-tmchweb01-disk01</v>
+        <v>-disk01</v>
       </c>
       <c r="H63" s="73" t="s">
         <v>181</v>
@@ -21050,7 +20903,7 @@
       </c>
       <c r="J63" s="73" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-tmchweb01-disk02</v>
+        <v>-disk02</v>
       </c>
       <c r="K63" s="73" t="s">
         <v>181</v>
@@ -21079,22 +20932,18 @@
       <c r="B64" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C64" s="74" t="str" cm="1">
+      <c r="C64" s="74" t="e" cm="1">
         <f t="array" ref="C64">UPPER(INDEX(_xlfn.TEXTSPLIT($D64, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="D64" s="74" t="s">
-        <v>286</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D64" s="74"/>
       <c r="E64" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F64" s="74" t="s">
-        <v>618</v>
-      </c>
+      <c r="F64" s="74"/>
       <c r="G64" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-dis-tmchap01-disk01</v>
+        <v>-disk01</v>
       </c>
       <c r="H64" s="74" t="s">
         <v>181</v>
@@ -21104,7 +20953,7 @@
       </c>
       <c r="J64" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-tmchap01-disk02</v>
+        <v>-disk02</v>
       </c>
       <c r="K64" s="74" t="s">
         <v>181</v>
@@ -21133,22 +20982,18 @@
       <c r="B65" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="C65" s="73" t="str" cm="1">
+      <c r="C65" s="73" t="e" cm="1">
         <f t="array" ref="C65">UPPER(INDEX(_xlfn.TEXTSPLIT($D65, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="D65" s="73" t="s">
-        <v>286</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D65" s="73"/>
       <c r="E65" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="F65" s="73" t="s">
-        <v>619</v>
-      </c>
+      <c r="F65" s="73"/>
       <c r="G65" s="73" t="str">
         <f t="shared" si="4"/>
-        <v>t-dis-tmchintweb01-disk01</v>
+        <v>-disk01</v>
       </c>
       <c r="H65" s="73" t="s">
         <v>181</v>
@@ -21158,7 +21003,7 @@
       </c>
       <c r="J65" s="73" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-tmchintweb01-disk02</v>
+        <v>-disk02</v>
       </c>
       <c r="K65" s="73" t="s">
         <v>181</v>
@@ -21187,22 +21032,18 @@
       <c r="B66" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C66" s="74" t="str" cm="1">
+      <c r="C66" s="74" t="e" cm="1">
         <f t="array" ref="C66">UPPER(INDEX(_xlfn.TEXTSPLIT($D66, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="D66" s="74" t="s">
-        <v>286</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D66" s="74"/>
       <c r="E66" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F66" s="74" t="s">
-        <v>620</v>
-      </c>
+      <c r="F66" s="74"/>
       <c r="G66" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-dis-gaoweb01-disk01</v>
+        <v>-disk01</v>
       </c>
       <c r="H66" s="74" t="s">
         <v>181</v>
@@ -21212,7 +21053,7 @@
       </c>
       <c r="J66" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-gaoweb01-disk02</v>
+        <v>-disk02</v>
       </c>
       <c r="K66" s="74" t="s">
         <v>181</v>
@@ -21241,22 +21082,18 @@
       <c r="B67" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="C67" s="73" t="str" cm="1">
+      <c r="C67" s="73" t="e" cm="1">
         <f t="array" ref="C67">UPPER(INDEX(_xlfn.TEXTSPLIT($D67, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="D67" s="73" t="s">
-        <v>286</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D67" s="73"/>
       <c r="E67" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="F67" s="73" t="s">
-        <v>621</v>
-      </c>
+      <c r="F67" s="73"/>
       <c r="G67" s="73" t="str">
         <f t="shared" si="4"/>
-        <v>t-dis-gaoap01-disk01</v>
+        <v>-disk01</v>
       </c>
       <c r="H67" s="73" t="s">
         <v>181</v>
@@ -21266,7 +21103,7 @@
       </c>
       <c r="J67" s="73" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-gaoap01-disk02</v>
+        <v>-disk02</v>
       </c>
       <c r="K67" s="73" t="s">
         <v>181</v>
@@ -23644,20 +23481,19 @@
       <c r="M60" s="73"/>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A61" s="97"/>
+      <c r="A61" s="117"/>
       <c r="B61" s="82" t="s">
         <v>182</v>
       </c>
       <c r="C61" s="82" t="str" cm="1">
         <f t="array" ref="C61">UPPER(INDEX(_xlfn.TEXTSPLIT($E61, "-"), 2))</f>
-        <v>DIP</v>
+        <v>CLV</v>
       </c>
       <c r="D61" s="82" t="s">
         <v>198</v>
       </c>
-      <c r="E61" s="82" t="str">
-        <f t="shared" si="4"/>
-        <v>t-dip-db-nsg</v>
+      <c r="E61" s="82" t="s">
+        <v>600</v>
       </c>
       <c r="F61" s="82" t="s">
         <v>198</v>
@@ -23666,7 +23502,7 @@
         <v>450</v>
       </c>
       <c r="H61" s="74" t="s">
-        <v>316</v>
+        <v>600</v>
       </c>
       <c r="I61" s="74"/>
       <c r="J61" s="74"/>
@@ -23677,20 +23513,19 @@
       <c r="M61" s="74"/>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A62" s="97"/>
+      <c r="A62" s="117"/>
       <c r="B62" s="80" t="s">
         <v>182</v>
       </c>
       <c r="C62" s="80" t="str" cm="1">
         <f t="array" ref="C62">UPPER(INDEX(_xlfn.TEXTSPLIT($E62, "-"), 2))</f>
-        <v>DIP</v>
+        <v>CLV</v>
       </c>
       <c r="D62" s="80" t="s">
         <v>198</v>
       </c>
-      <c r="E62" s="80" t="str">
-        <f t="shared" si="4"/>
-        <v>t-dip-pe-nsg</v>
+      <c r="E62" s="80" t="s">
+        <v>601</v>
       </c>
       <c r="F62" s="80" t="s">
         <v>198</v>
@@ -23699,7 +23534,7 @@
         <v>450</v>
       </c>
       <c r="H62" s="73" t="s">
-        <v>317</v>
+        <v>601</v>
       </c>
       <c r="I62" s="73"/>
       <c r="J62" s="73"/>
@@ -24202,20 +24037,20 @@
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A76" s="97"/>
+      <c r="A76" s="117"/>
       <c r="B76" s="82" t="s">
         <v>182</v>
       </c>
       <c r="C76" s="82" t="str" cm="1">
         <f t="array" ref="C76">UPPER(INDEX(_xlfn.TEXTSPLIT($E76, "-"), 2))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D76" s="82" t="s">
         <v>198</v>
       </c>
       <c r="E76" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>t-dis-clvweb01-nsg</v>
+        <v>t-clv-web01-nsg</v>
       </c>
       <c r="F76" s="82" t="s">
         <v>198</v>
@@ -24224,17 +24059,17 @@
         <v>199</v>
       </c>
       <c r="H76" s="82" t="s">
-        <v>290</v>
+        <v>598</v>
       </c>
       <c r="I76" s="82" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="J76" s="82" t="s">
-        <v>286</v>
+        <v>597</v>
       </c>
       <c r="K76" s="82" t="str">
         <f t="shared" ref="K76:K80" si="8">SUBSTITUTE(I76,"hazr-","")&amp;"-nic"</f>
-        <v>t-dis-clvweb01-nic</v>
+        <v>t-clv-web01-nic</v>
       </c>
       <c r="L76" s="82" t="s">
         <v>516</v>
@@ -24242,20 +24077,20 @@
       <c r="M76" s="82"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A77" s="97"/>
+      <c r="A77" s="117"/>
       <c r="B77" s="80" t="s">
         <v>182</v>
       </c>
       <c r="C77" s="80" t="str" cm="1">
         <f t="array" ref="C77">UPPER(INDEX(_xlfn.TEXTSPLIT($E77, "-"), 2))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D77" s="80" t="s">
         <v>198</v>
       </c>
       <c r="E77" s="80" t="str">
         <f t="shared" si="7"/>
-        <v>t-dis-clvap01-nsg</v>
+        <v>t-clv-ap01-nsg</v>
       </c>
       <c r="F77" s="80" t="s">
         <v>198</v>
@@ -24264,17 +24099,17 @@
         <v>200</v>
       </c>
       <c r="H77" s="80" t="s">
-        <v>288</v>
+        <v>599</v>
       </c>
       <c r="I77" s="80" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="J77" s="80" t="s">
-        <v>286</v>
+        <v>597</v>
       </c>
       <c r="K77" s="80" t="str">
         <f t="shared" si="8"/>
-        <v>t-dis-clvap01-nic</v>
+        <v>t-clv-ap01-nic</v>
       </c>
       <c r="L77" s="80" t="s">
         <v>516</v>
@@ -24282,20 +24117,20 @@
       <c r="M77" s="80"/>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A78" s="97"/>
+      <c r="A78" s="117"/>
       <c r="B78" s="82" t="s">
         <v>182</v>
       </c>
       <c r="C78" s="82" t="str" cm="1">
         <f t="array" ref="C78">UPPER(INDEX(_xlfn.TEXTSPLIT($E78, "-"), 2))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D78" s="82" t="s">
         <v>198</v>
       </c>
       <c r="E78" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>t-dis-clvssrap01-nsg</v>
+        <v>t-clv-ssrap01-nsg</v>
       </c>
       <c r="F78" s="82" t="s">
         <v>198</v>
@@ -24304,17 +24139,17 @@
         <v>200</v>
       </c>
       <c r="H78" s="82" t="s">
-        <v>288</v>
+        <v>599</v>
       </c>
       <c r="I78" s="82" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J78" s="82" t="s">
-        <v>286</v>
+        <v>597</v>
       </c>
       <c r="K78" s="82" t="str">
         <f t="shared" si="8"/>
-        <v>t-dis-clvssrap01-nic</v>
+        <v>t-clv-ssrap01-nic</v>
       </c>
       <c r="L78" s="82" t="s">
         <v>516</v>
@@ -24322,20 +24157,20 @@
       <c r="M78" s="82"/>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A79" s="97"/>
+      <c r="A79" s="117"/>
       <c r="B79" s="80" t="s">
         <v>182</v>
       </c>
       <c r="C79" s="80" t="str" cm="1">
         <f t="array" ref="C79">UPPER(INDEX(_xlfn.TEXTSPLIT($E79, "-"), 2))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D79" s="80" t="s">
         <v>198</v>
       </c>
       <c r="E79" s="80" t="str">
         <f t="shared" si="7"/>
-        <v>t-dis-clvadmweb01-nsg</v>
+        <v>t-clv-admweb01-nsg</v>
       </c>
       <c r="F79" s="80" t="s">
         <v>198</v>
@@ -24344,17 +24179,17 @@
         <v>200</v>
       </c>
       <c r="H79" s="80" t="s">
-        <v>288</v>
+        <v>599</v>
       </c>
       <c r="I79" s="80" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="J79" s="80" t="s">
-        <v>286</v>
+        <v>597</v>
       </c>
       <c r="K79" s="80" t="str">
         <f t="shared" si="8"/>
-        <v>t-dis-clvadmweb01-nic</v>
+        <v>t-clv-admweb01-nic</v>
       </c>
       <c r="L79" s="80" t="s">
         <v>516</v>
@@ -24362,20 +24197,20 @@
       <c r="M79" s="80"/>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A80" s="97"/>
+      <c r="A80" s="117"/>
       <c r="B80" s="82" t="s">
         <v>182</v>
       </c>
       <c r="C80" s="82" t="str" cm="1">
         <f t="array" ref="C80">UPPER(INDEX(_xlfn.TEXTSPLIT($E80, "-"), 2))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D80" s="82" t="s">
         <v>198</v>
       </c>
       <c r="E80" s="82" t="str">
         <f t="shared" si="7"/>
-        <v>t-dis-clvadmap01-nsg</v>
+        <v>t-clv-admap01-nsg</v>
       </c>
       <c r="F80" s="82" t="s">
         <v>198</v>
@@ -24384,17 +24219,17 @@
         <v>200</v>
       </c>
       <c r="H80" s="82" t="s">
-        <v>288</v>
+        <v>599</v>
       </c>
       <c r="I80" s="82" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="J80" s="82" t="s">
-        <v>286</v>
+        <v>597</v>
       </c>
       <c r="K80" s="82" t="str">
         <f t="shared" si="8"/>
-        <v>t-dis-clvadmap01-nic</v>
+        <v>t-clv-admap01-nic</v>
       </c>
       <c r="L80" s="82" t="s">
         <v>516</v>
@@ -24405,17 +24240,14 @@
       <c r="B81" s="80" t="s">
         <v>182</v>
       </c>
-      <c r="C81" s="80" t="str" cm="1">
+      <c r="C81" s="80" t="e" cm="1">
         <f t="array" ref="C81">UPPER(INDEX(_xlfn.TEXTSPLIT($E81, "-"), 2))</f>
-        <v>DIS</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D81" s="80" t="s">
         <v>198</v>
       </c>
-      <c r="E81" s="80" t="str">
-        <f t="shared" si="7"/>
-        <v>t-dis-tmchweb01-nsg</v>
-      </c>
+      <c r="E81" s="80"/>
       <c r="F81" s="80" t="s">
         <v>198</v>
       </c>
@@ -24425,15 +24257,11 @@
       <c r="H81" s="80" t="s">
         <v>290</v>
       </c>
-      <c r="I81" s="80" t="s">
-        <v>617</v>
-      </c>
-      <c r="J81" s="80" t="s">
-        <v>286</v>
-      </c>
+      <c r="I81" s="80"/>
+      <c r="J81" s="80"/>
       <c r="K81" s="80" t="str">
         <f t="shared" ref="K81:K85" si="9">SUBSTITUTE(I81,"hazr-","")&amp;"-nic"</f>
-        <v>t-dis-tmchweb01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="L81" s="80" t="s">
         <v>516</v>
@@ -24444,17 +24272,14 @@
       <c r="B82" s="82" t="s">
         <v>182</v>
       </c>
-      <c r="C82" s="82" t="str" cm="1">
+      <c r="C82" s="82" t="e" cm="1">
         <f t="array" ref="C82">UPPER(INDEX(_xlfn.TEXTSPLIT($E82, "-"), 2))</f>
-        <v>DIS</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D82" s="82" t="s">
         <v>198</v>
       </c>
-      <c r="E82" s="82" t="str">
-        <f t="shared" si="7"/>
-        <v>t-dis-tmchap01-nsg</v>
-      </c>
+      <c r="E82" s="82"/>
       <c r="F82" s="82" t="s">
         <v>198</v>
       </c>
@@ -24464,15 +24289,11 @@
       <c r="H82" s="82" t="s">
         <v>288</v>
       </c>
-      <c r="I82" s="82" t="s">
-        <v>618</v>
-      </c>
-      <c r="J82" s="82" t="s">
-        <v>286</v>
-      </c>
+      <c r="I82" s="82"/>
+      <c r="J82" s="82"/>
       <c r="K82" s="82" t="str">
         <f t="shared" si="9"/>
-        <v>t-dis-tmchap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="L82" s="82" t="s">
         <v>516</v>
@@ -24483,17 +24304,14 @@
       <c r="B83" s="80" t="s">
         <v>182</v>
       </c>
-      <c r="C83" s="80" t="str" cm="1">
+      <c r="C83" s="80" t="e" cm="1">
         <f t="array" ref="C83">UPPER(INDEX(_xlfn.TEXTSPLIT($E83, "-"), 2))</f>
-        <v>DIS</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D83" s="80" t="s">
         <v>198</v>
       </c>
-      <c r="E83" s="80" t="str">
-        <f t="shared" si="7"/>
-        <v>t-dis-tmchintweb01-nsg</v>
-      </c>
+      <c r="E83" s="80"/>
       <c r="F83" s="80" t="s">
         <v>198</v>
       </c>
@@ -24503,15 +24321,11 @@
       <c r="H83" s="80" t="s">
         <v>288</v>
       </c>
-      <c r="I83" s="80" t="s">
-        <v>619</v>
-      </c>
-      <c r="J83" s="80" t="s">
-        <v>286</v>
-      </c>
+      <c r="I83" s="80"/>
+      <c r="J83" s="80"/>
       <c r="K83" s="80" t="str">
         <f t="shared" si="9"/>
-        <v>t-dis-tmchintweb01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="L83" s="80" t="s">
         <v>516</v>
@@ -24522,17 +24336,14 @@
       <c r="B84" s="82" t="s">
         <v>182</v>
       </c>
-      <c r="C84" s="82" t="str" cm="1">
+      <c r="C84" s="82" t="e" cm="1">
         <f t="array" ref="C84">UPPER(INDEX(_xlfn.TEXTSPLIT($E84, "-"), 2))</f>
-        <v>DIS</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D84" s="82" t="s">
         <v>198</v>
       </c>
-      <c r="E84" s="82" t="str">
-        <f t="shared" si="7"/>
-        <v>t-dis-gaoweb01-nsg</v>
-      </c>
+      <c r="E84" s="82"/>
       <c r="F84" s="82" t="s">
         <v>198</v>
       </c>
@@ -24542,15 +24353,11 @@
       <c r="H84" s="82" t="s">
         <v>290</v>
       </c>
-      <c r="I84" s="82" t="s">
-        <v>620</v>
-      </c>
-      <c r="J84" s="82" t="s">
-        <v>286</v>
-      </c>
+      <c r="I84" s="82"/>
+      <c r="J84" s="82"/>
       <c r="K84" s="82" t="str">
         <f t="shared" si="9"/>
-        <v>t-dis-gaoweb01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="L84" s="82" t="s">
         <v>516</v>
@@ -24561,17 +24368,14 @@
       <c r="B85" s="80" t="s">
         <v>182</v>
       </c>
-      <c r="C85" s="80" t="str" cm="1">
+      <c r="C85" s="80" t="e" cm="1">
         <f t="array" ref="C85">UPPER(INDEX(_xlfn.TEXTSPLIT($E85, "-"), 2))</f>
-        <v>DIS</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D85" s="80" t="s">
         <v>198</v>
       </c>
-      <c r="E85" s="80" t="str">
-        <f t="shared" si="7"/>
-        <v>t-dis-gaoap01-nsg</v>
-      </c>
+      <c r="E85" s="80"/>
       <c r="F85" s="80" t="s">
         <v>198</v>
       </c>
@@ -24581,15 +24385,11 @@
       <c r="H85" s="80" t="s">
         <v>288</v>
       </c>
-      <c r="I85" s="80" t="s">
-        <v>621</v>
-      </c>
-      <c r="J85" s="80" t="s">
-        <v>286</v>
-      </c>
+      <c r="I85" s="80"/>
+      <c r="J85" s="80"/>
       <c r="K85" s="80" t="str">
         <f t="shared" si="9"/>
-        <v>t-dis-gaoap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="L85" s="80" t="s">
         <v>516</v>
@@ -29221,13 +29021,13 @@
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A41" s="97"/>
+      <c r="A41" s="117"/>
       <c r="B41" s="84" t="s">
         <v>182</v>
       </c>
       <c r="C41" s="84" t="str" cm="1">
         <f t="array" ref="C41">UPPER(INDEX(_xlfn.TEXTSPLIT($F41, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D41" s="84" t="s">
         <v>286</v>
@@ -29236,7 +29036,7 @@
         <v>24</v>
       </c>
       <c r="F41" s="84" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="G41" s="84" t="s">
         <v>111</v>
@@ -29252,7 +29052,7 @@
       </c>
       <c r="K41" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-dis-clvweb-lb-fe</v>
+        <v>t-clv-web-lb-fe</v>
       </c>
       <c r="L41" s="84" t="s">
         <v>198</v>
@@ -29261,27 +29061,27 @@
         <v>199</v>
       </c>
       <c r="N41" s="84" t="s">
-        <v>290</v>
+        <v>598</v>
       </c>
       <c r="O41" s="84" t="s">
         <v>108</v>
       </c>
       <c r="P41" s="84" t="s">
-        <v>596</v>
+        <v>607</v>
       </c>
       <c r="Q41" s="85" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-clvweb-lb-bp</v>
+        <v>t-clv-web-lb-bp</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A42" s="97"/>
+      <c r="A42" s="117"/>
       <c r="B42" s="74" t="s">
         <v>182</v>
       </c>
       <c r="C42" s="74" t="str" cm="1">
         <f t="array" ref="C42">UPPER(INDEX(_xlfn.TEXTSPLIT($F42, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D42" s="74" t="s">
         <v>286</v>
@@ -29290,7 +29090,7 @@
         <v>24</v>
       </c>
       <c r="F42" s="74" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="G42" s="74" t="s">
         <v>111</v>
@@ -29306,7 +29106,7 @@
       </c>
       <c r="K42" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-dis-clvap-lb-fe</v>
+        <v>t-clv-ap-lb-fe</v>
       </c>
       <c r="L42" s="74" t="s">
         <v>198</v>
@@ -29315,27 +29115,27 @@
         <v>200</v>
       </c>
       <c r="N42" s="74" t="s">
-        <v>288</v>
+        <v>599</v>
       </c>
       <c r="O42" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P42" s="74" t="s">
-        <v>598</v>
+        <v>608</v>
       </c>
       <c r="Q42" s="87" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-clvap-lb-bp</v>
+        <v>t-clv-ap-lb-bp</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A43" s="97"/>
+      <c r="A43" s="117"/>
       <c r="B43" s="84" t="s">
         <v>182</v>
       </c>
       <c r="C43" s="84" t="str" cm="1">
         <f t="array" ref="C43">UPPER(INDEX(_xlfn.TEXTSPLIT($F43, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D43" s="84" t="s">
         <v>286</v>
@@ -29344,7 +29144,7 @@
         <v>24</v>
       </c>
       <c r="F43" s="84" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="G43" s="84" t="s">
         <v>111</v>
@@ -29360,7 +29160,7 @@
       </c>
       <c r="K43" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-dis-clvssrap-lb-fe</v>
+        <v>t-clv-ssrap-lb-fe</v>
       </c>
       <c r="L43" s="84" t="s">
         <v>198</v>
@@ -29369,27 +29169,27 @@
         <v>200</v>
       </c>
       <c r="N43" s="84" t="s">
-        <v>288</v>
+        <v>599</v>
       </c>
       <c r="O43" s="84" t="s">
         <v>108</v>
       </c>
       <c r="P43" s="84" t="s">
-        <v>600</v>
+        <v>609</v>
       </c>
       <c r="Q43" s="85" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-clvssrap-lb-bp</v>
+        <v>t-clv-ssrap-lb-bp</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A44" s="97"/>
+      <c r="A44" s="117"/>
       <c r="B44" s="107" t="s">
         <v>182</v>
       </c>
       <c r="C44" s="107" t="str" cm="1">
         <f t="array" ref="C44">UPPER(INDEX(_xlfn.TEXTSPLIT($F44, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D44" s="107" t="s">
         <v>286</v>
@@ -29398,7 +29198,7 @@
         <v>24</v>
       </c>
       <c r="F44" s="107" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="G44" s="107" t="s">
         <v>111</v>
@@ -29414,7 +29214,7 @@
       </c>
       <c r="K44" s="107" t="str">
         <f t="shared" si="4"/>
-        <v>t-dis-clvadmweb-lb-fe</v>
+        <v>t-clv-admweb-lb-fe</v>
       </c>
       <c r="L44" s="107" t="s">
         <v>198</v>
@@ -29423,27 +29223,27 @@
         <v>200</v>
       </c>
       <c r="N44" s="107" t="s">
-        <v>288</v>
+        <v>599</v>
       </c>
       <c r="O44" s="107" t="s">
         <v>108</v>
       </c>
       <c r="P44" s="107" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="Q44" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-clvadmweb-lb-bp</v>
+        <v>t-clv-admweb-lb-bp</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A45" s="69"/>
+      <c r="A45" s="119"/>
       <c r="B45" s="84" t="s">
         <v>182</v>
       </c>
       <c r="C45" s="84" t="str" cm="1">
         <f t="array" ref="C45">UPPER(INDEX(_xlfn.TEXTSPLIT($F45, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D45" s="84" t="s">
         <v>286</v>
@@ -29452,7 +29252,7 @@
         <v>24</v>
       </c>
       <c r="F45" s="84" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="G45" s="84" t="s">
         <v>111</v>
@@ -29468,7 +29268,7 @@
       </c>
       <c r="K45" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-dis-clvadmap-lb-fe</v>
+        <v>t-clv-admap-lb-fe</v>
       </c>
       <c r="L45" s="84" t="s">
         <v>198</v>
@@ -29477,17 +29277,17 @@
         <v>200</v>
       </c>
       <c r="N45" s="84" t="s">
-        <v>288</v>
+        <v>599</v>
       </c>
       <c r="O45" s="84" t="s">
         <v>108</v>
       </c>
       <c r="P45" s="84" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="Q45" s="85" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-clvadmap-lb-bp</v>
+        <v>t-clv-admap-lb-bp</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
@@ -29495,9 +29295,9 @@
       <c r="B46" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C46" s="74" t="str" cm="1">
+      <c r="C46" s="74" t="e" cm="1">
         <f t="array" ref="C46">UPPER(INDEX(_xlfn.TEXTSPLIT($F46, "-"), 3))</f>
-        <v>DIS</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D46" s="74" t="s">
         <v>286</v>
@@ -29505,9 +29305,7 @@
       <c r="E46" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F46" s="74" t="s">
-        <v>622</v>
-      </c>
+      <c r="F46" s="74"/>
       <c r="G46" s="74" t="s">
         <v>111</v>
       </c>
@@ -29515,14 +29313,14 @@
         <v>538</v>
       </c>
       <c r="I46" s="74" t="s">
-        <v>627</v>
+        <v>582</v>
       </c>
       <c r="J46" s="74" t="s">
         <v>102</v>
       </c>
       <c r="K46" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-dis-tmchweb-lb-fe</v>
+        <v>-fe</v>
       </c>
       <c r="L46" s="74" t="s">
         <v>198</v>
@@ -29530,18 +29328,14 @@
       <c r="M46" s="74" t="s">
         <v>199</v>
       </c>
-      <c r="N46" s="74" t="s">
-        <v>290</v>
-      </c>
+      <c r="N46" s="74"/>
       <c r="O46" s="74" t="s">
         <v>108</v>
       </c>
-      <c r="P46" s="74" t="s">
-        <v>629</v>
-      </c>
+      <c r="P46" s="74"/>
       <c r="Q46" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-tmchweb-lb-bp</v>
+        <v>-bp</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
@@ -29549,9 +29343,9 @@
       <c r="B47" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C47" s="84" t="str" cm="1">
+      <c r="C47" s="84" t="e" cm="1">
         <f t="array" ref="C47">UPPER(INDEX(_xlfn.TEXTSPLIT($F47, "-"), 3))</f>
-        <v>DIS</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D47" s="84" t="s">
         <v>286</v>
@@ -29559,9 +29353,7 @@
       <c r="E47" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="F47" s="84" t="s">
-        <v>623</v>
-      </c>
+      <c r="F47" s="84"/>
       <c r="G47" s="84" t="s">
         <v>111</v>
       </c>
@@ -29569,14 +29361,14 @@
         <v>538</v>
       </c>
       <c r="I47" s="84" t="s">
-        <v>627</v>
+        <v>582</v>
       </c>
       <c r="J47" s="84" t="s">
         <v>102</v>
       </c>
       <c r="K47" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-dis-tmchap-lb-fe</v>
+        <v>-fe</v>
       </c>
       <c r="L47" s="84" t="s">
         <v>198</v>
@@ -29584,18 +29376,14 @@
       <c r="M47" s="84" t="s">
         <v>200</v>
       </c>
-      <c r="N47" s="84" t="s">
-        <v>288</v>
-      </c>
+      <c r="N47" s="84"/>
       <c r="O47" s="84" t="s">
         <v>108</v>
       </c>
-      <c r="P47" s="84" t="s">
-        <v>630</v>
-      </c>
+      <c r="P47" s="84"/>
       <c r="Q47" s="85" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-tmchap-lb-bp</v>
+        <v>-bp</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
@@ -29603,9 +29391,9 @@
       <c r="B48" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C48" s="74" t="str" cm="1">
+      <c r="C48" s="74" t="e" cm="1">
         <f t="array" ref="C48">UPPER(INDEX(_xlfn.TEXTSPLIT($F48, "-"), 3))</f>
-        <v>DIS</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D48" s="74" t="s">
         <v>286</v>
@@ -29613,9 +29401,7 @@
       <c r="E48" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F48" s="74" t="s">
-        <v>624</v>
-      </c>
+      <c r="F48" s="74"/>
       <c r="G48" s="74" t="s">
         <v>111</v>
       </c>
@@ -29623,14 +29409,14 @@
         <v>538</v>
       </c>
       <c r="I48" s="74" t="s">
-        <v>627</v>
+        <v>582</v>
       </c>
       <c r="J48" s="74" t="s">
         <v>102</v>
       </c>
       <c r="K48" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-dis-tmchintweb-lb-fe</v>
+        <v>-fe</v>
       </c>
       <c r="L48" s="74" t="s">
         <v>198</v>
@@ -29638,18 +29424,14 @@
       <c r="M48" s="74" t="s">
         <v>200</v>
       </c>
-      <c r="N48" s="74" t="s">
-        <v>628</v>
-      </c>
+      <c r="N48" s="74"/>
       <c r="O48" s="74" t="s">
         <v>108</v>
       </c>
-      <c r="P48" s="74" t="s">
-        <v>631</v>
-      </c>
+      <c r="P48" s="74"/>
       <c r="Q48" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-tmchintweb-lb-bp</v>
+        <v>-bp</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.3">
@@ -29657,9 +29439,9 @@
       <c r="B49" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C49" s="84" t="str" cm="1">
+      <c r="C49" s="84" t="e" cm="1">
         <f t="array" ref="C49">UPPER(INDEX(_xlfn.TEXTSPLIT($F49, "-"), 3))</f>
-        <v>DIS</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D49" s="84" t="s">
         <v>286</v>
@@ -29667,9 +29449,7 @@
       <c r="E49" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="F49" s="84" t="s">
-        <v>625</v>
-      </c>
+      <c r="F49" s="84"/>
       <c r="G49" s="84" t="s">
         <v>111</v>
       </c>
@@ -29677,14 +29457,14 @@
         <v>538</v>
       </c>
       <c r="I49" s="84" t="s">
-        <v>627</v>
+        <v>582</v>
       </c>
       <c r="J49" s="84" t="s">
         <v>102</v>
       </c>
       <c r="K49" s="84" t="str">
         <f t="shared" si="4"/>
-        <v>t-dis-gaoweb-lb-fe</v>
+        <v>-fe</v>
       </c>
       <c r="L49" s="84" t="s">
         <v>198</v>
@@ -29692,18 +29472,14 @@
       <c r="M49" s="84" t="s">
         <v>199</v>
       </c>
-      <c r="N49" s="84" t="s">
-        <v>290</v>
-      </c>
+      <c r="N49" s="84"/>
       <c r="O49" s="84" t="s">
         <v>108</v>
       </c>
-      <c r="P49" s="84" t="s">
-        <v>632</v>
-      </c>
+      <c r="P49" s="84"/>
       <c r="Q49" s="85" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-gaoweb-lb-bp</v>
+        <v>-bp</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.3">
@@ -29711,9 +29487,9 @@
       <c r="B50" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C50" s="74" t="str" cm="1">
+      <c r="C50" s="74" t="e" cm="1">
         <f t="array" ref="C50">UPPER(INDEX(_xlfn.TEXTSPLIT($F50, "-"), 3))</f>
-        <v>DIS</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D50" s="74" t="s">
         <v>286</v>
@@ -29721,9 +29497,7 @@
       <c r="E50" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F50" s="74" t="s">
-        <v>626</v>
-      </c>
+      <c r="F50" s="74"/>
       <c r="G50" s="74" t="s">
         <v>111</v>
       </c>
@@ -29731,14 +29505,14 @@
         <v>538</v>
       </c>
       <c r="I50" s="74" t="s">
-        <v>627</v>
+        <v>582</v>
       </c>
       <c r="J50" s="74" t="s">
         <v>102</v>
       </c>
       <c r="K50" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-dis-gaoap-lb-fe</v>
+        <v>-fe</v>
       </c>
       <c r="L50" s="74" t="s">
         <v>198</v>
@@ -29746,18 +29520,14 @@
       <c r="M50" s="74" t="s">
         <v>200</v>
       </c>
-      <c r="N50" s="74" t="s">
-        <v>628</v>
-      </c>
+      <c r="N50" s="74"/>
       <c r="O50" s="74" t="s">
         <v>108</v>
       </c>
-      <c r="P50" s="74" t="s">
-        <v>633</v>
-      </c>
+      <c r="P50" s="74"/>
       <c r="Q50" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-gaoap-lb-bp</v>
+        <v>-bp</v>
       </c>
     </row>
   </sheetData>
@@ -31891,26 +31661,26 @@
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A66" s="69"/>
+      <c r="A66" s="119"/>
       <c r="B66" s="84" t="s">
         <v>182</v>
       </c>
       <c r="C66" s="84" t="str" cm="1">
         <f t="array" ref="C66">UPPER(INDEX(_xlfn.TEXTSPLIT($D66, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D66" s="84" t="s">
-        <v>286</v>
+        <v>585</v>
       </c>
       <c r="E66" s="84" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="F66" s="84" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-clvweb-lb-pb443</v>
+        <v>t-clv-web-lb-pb443</v>
       </c>
       <c r="G66" s="84" t="s">
-        <v>605</v>
+        <v>576</v>
       </c>
       <c r="H66" s="84">
         <v>443</v>
@@ -31924,26 +31694,26 @@
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A67" s="69"/>
+      <c r="A67" s="119"/>
       <c r="B67" s="74" t="s">
         <v>182</v>
       </c>
       <c r="C67" s="74" t="str" cm="1">
         <f t="array" ref="C67">UPPER(INDEX(_xlfn.TEXTSPLIT($D67, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D67" s="74" t="s">
-        <v>286</v>
+        <v>585</v>
       </c>
       <c r="E67" s="74" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="F67" s="74" t="str">
         <f t="shared" si="6"/>
-        <v>t-dis-clvap-lb-pb8080</v>
+        <v>t-clv-ap-lb-pb8080</v>
       </c>
       <c r="G67" s="74" t="s">
-        <v>605</v>
+        <v>576</v>
       </c>
       <c r="H67" s="74">
         <v>8080</v>
@@ -31957,26 +31727,26 @@
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A68" s="69"/>
+      <c r="A68" s="119"/>
       <c r="B68" s="84" t="s">
         <v>182</v>
       </c>
       <c r="C68" s="84" t="str" cm="1">
         <f t="array" ref="C68">UPPER(INDEX(_xlfn.TEXTSPLIT($D68, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D68" s="84" t="s">
-        <v>286</v>
+        <v>585</v>
       </c>
       <c r="E68" s="84" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="F68" s="84" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-clvssrap-lb-pb8080</v>
+        <v>t-clv-ssrap-lb-pb8080</v>
       </c>
       <c r="G68" s="84" t="s">
-        <v>605</v>
+        <v>576</v>
       </c>
       <c r="H68" s="84">
         <v>8080</v>
@@ -31990,26 +31760,26 @@
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A69" s="69"/>
+      <c r="A69" s="119"/>
       <c r="B69" s="74" t="s">
         <v>182</v>
       </c>
       <c r="C69" s="74" t="str" cm="1">
         <f t="array" ref="C69">UPPER(INDEX(_xlfn.TEXTSPLIT($D69, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D69" s="74" t="s">
-        <v>286</v>
-      </c>
-      <c r="E69" s="74" t="s">
-        <v>601</v>
+        <v>585</v>
+      </c>
+      <c r="E69" s="107" t="s">
+        <v>605</v>
       </c>
       <c r="F69" s="74" t="str">
         <f t="shared" si="6"/>
-        <v>t-dis-clvadmweb-lb-pb443</v>
+        <v>t-clv-admweb-lb-pb443</v>
       </c>
       <c r="G69" s="74" t="s">
-        <v>605</v>
+        <v>576</v>
       </c>
       <c r="H69" s="74">
         <v>443</v>
@@ -32023,26 +31793,26 @@
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A70" s="69"/>
+      <c r="A70" s="119"/>
       <c r="B70" s="84" t="s">
         <v>182</v>
       </c>
       <c r="C70" s="84" t="str" cm="1">
         <f t="array" ref="C70">UPPER(INDEX(_xlfn.TEXTSPLIT($D70, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D70" s="84" t="s">
-        <v>286</v>
+        <v>585</v>
       </c>
       <c r="E70" s="84" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="F70" s="84" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-clvadmap-lb-pb8080</v>
+        <v>t-clv-admap-lb-pb8080</v>
       </c>
       <c r="G70" s="84" t="s">
-        <v>605</v>
+        <v>576</v>
       </c>
       <c r="H70" s="84">
         <v>8080</v>
@@ -32060,22 +31830,18 @@
       <c r="B71" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C71" s="74" t="str" cm="1">
+      <c r="C71" s="74" t="e" cm="1">
         <f t="array" ref="C71">UPPER(INDEX(_xlfn.TEXTSPLIT($D71, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="D71" s="74" t="s">
-        <v>286</v>
-      </c>
-      <c r="E71" s="74" t="s">
-        <v>622</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D71" s="74"/>
+      <c r="E71" s="74"/>
       <c r="F71" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-tmchweb-lb-pb443</v>
+        <v>-pb443</v>
       </c>
       <c r="G71" s="74" t="s">
-        <v>634</v>
+        <v>583</v>
       </c>
       <c r="H71" s="74">
         <v>443</v>
@@ -32093,22 +31859,18 @@
       <c r="B72" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C72" s="84" t="str" cm="1">
+      <c r="C72" s="84" t="e" cm="1">
         <f t="array" ref="C72">UPPER(INDEX(_xlfn.TEXTSPLIT($D72, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="D72" s="84" t="s">
-        <v>286</v>
-      </c>
-      <c r="E72" s="84" t="s">
-        <v>623</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D72" s="84"/>
+      <c r="E72" s="84"/>
       <c r="F72" s="84" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-tmchap-lb-pb8080</v>
+        <v>-pb8080</v>
       </c>
       <c r="G72" s="84" t="s">
-        <v>634</v>
+        <v>583</v>
       </c>
       <c r="H72" s="84">
         <v>8080</v>
@@ -32126,22 +31888,18 @@
       <c r="B73" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C73" s="74" t="str" cm="1">
+      <c r="C73" s="74" t="e" cm="1">
         <f t="array" ref="C73">UPPER(INDEX(_xlfn.TEXTSPLIT($D73, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="D73" s="74" t="s">
-        <v>286</v>
-      </c>
-      <c r="E73" s="74" t="s">
-        <v>624</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D73" s="74"/>
+      <c r="E73" s="74"/>
       <c r="F73" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-tmchintweb-lb-pb443</v>
+        <v>-pb443</v>
       </c>
       <c r="G73" s="74" t="s">
-        <v>634</v>
+        <v>583</v>
       </c>
       <c r="H73" s="74">
         <v>443</v>
@@ -32159,22 +31917,18 @@
       <c r="B74" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="C74" s="84" t="str" cm="1">
+      <c r="C74" s="84" t="e" cm="1">
         <f t="array" ref="C74">UPPER(INDEX(_xlfn.TEXTSPLIT($D74, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="D74" s="84" t="s">
-        <v>286</v>
-      </c>
-      <c r="E74" s="84" t="s">
-        <v>625</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D74" s="84"/>
+      <c r="E74" s="84"/>
       <c r="F74" s="84" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-gaoweb-lb-pb443</v>
+        <v>-pb443</v>
       </c>
       <c r="G74" s="84" t="s">
-        <v>634</v>
+        <v>583</v>
       </c>
       <c r="H74" s="84">
         <v>443</v>
@@ -32192,22 +31946,18 @@
       <c r="B75" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="C75" s="74" t="str" cm="1">
+      <c r="C75" s="74" t="e" cm="1">
         <f t="array" ref="C75">UPPER(INDEX(_xlfn.TEXTSPLIT($D75, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="D75" s="74" t="s">
-        <v>286</v>
-      </c>
-      <c r="E75" s="74" t="s">
-        <v>626</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D75" s="74"/>
+      <c r="E75" s="74"/>
       <c r="F75" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-dis-gaoap-lb-pb8080</v>
+        <v>-pb8080</v>
       </c>
       <c r="G75" s="74" t="s">
-        <v>634</v>
+        <v>583</v>
       </c>
       <c r="H75" s="74">
         <v>8080</v>
@@ -32227,21 +31977,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -32385,31 +32120,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -32425,4 +32151,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>